--- a/Docmentations/TEAM_4_Project_Status_Report.xlsx
+++ b/Docmentations/TEAM_4_Project_Status_Report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Desktop\ITI-Config-project\iti-Config-managment\Docmentations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD1717C4-D2A7-4A97-A552-CCA1840CAA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA499B0-06DB-4DA8-8A66-B87BC3536687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
   <si>
     <t>Day</t>
   </si>
@@ -73,25 +73,7 @@
     <t>Mitigate</t>
   </si>
   <si>
-    <t>medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">high </t>
-  </si>
-  <si>
-    <t>Accept</t>
-  </si>
-  <si>
-    <t>R_2</t>
-  </si>
-  <si>
-    <t>Resource</t>
-  </si>
-  <si>
     <t>A team member is required to perform mandatory military service</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> reassign the member's tasks to others. adjust the project timeline </t>
   </si>
   <si>
     <t>Menna</t>
@@ -112,16 +94,7 @@
     <t xml:space="preserve">Mario </t>
   </si>
   <si>
-    <t>R_3</t>
-  </si>
-  <si>
-    <t>holidays</t>
-  </si>
-  <si>
     <t>high</t>
-  </si>
-  <si>
-    <t>There is a shortage within the team due to the Christian holidays</t>
   </si>
   <si>
     <t>Issue_ID_1</t>
@@ -130,58 +103,7 @@
     <t>reassign the member's tasks to others. adjust the project timeline</t>
   </si>
   <si>
-    <t>Issue_ID_2</t>
-  </si>
-  <si>
-    <t>Mario / Mena</t>
-  </si>
-  <si>
-    <t>Issue_ID_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">she had a connection problem remains for 2 days </t>
-  </si>
-  <si>
     <t>Points</t>
-  </si>
-  <si>
-    <t>Create ERD</t>
-  </si>
-  <si>
-    <t>Review ERD</t>
-  </si>
-  <si>
-    <t>Create Class Diagram</t>
-  </si>
-  <si>
-    <t>Review Class Diagram</t>
-  </si>
-  <si>
-    <t>create Sequence diagram</t>
-  </si>
-  <si>
-    <t>Review Sequence diagram</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create Global View </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review Global View </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create Flow Chart </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Review Flow Chart </t>
-  </si>
-  <si>
-    <t>Create WireFrame</t>
-  </si>
-  <si>
-    <t>Update RTM</t>
-  </si>
-  <si>
-    <t>Update SIQ</t>
   </si>
   <si>
     <t>Create Release Plan</t>
@@ -205,7 +127,19 @@
     <t>Mena</t>
   </si>
   <si>
-    <t>Review and Support in update  WireFrame</t>
+    <t xml:space="preserve">Create Backend </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code Review </t>
+  </si>
+  <si>
+    <t>Create Backend arch</t>
+  </si>
+  <si>
+    <t>Create Frontend JS {auth}</t>
+  </si>
+  <si>
+    <t>Create Frontend HTML CSS</t>
   </si>
 </sst>
 </file>
@@ -519,7 +453,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -590,10 +524,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -612,6 +542,11 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -703,25 +638,25 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>9</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>25</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>30</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>35</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -757,16 +692,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>9</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>14</c:v>
+                  <c:v>26</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -963,6 +898,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Release 3</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1066,22 +1026,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>12</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>16</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>56</c:v>
+                  <c:v>81</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1149,22 +1109,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>11</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>53</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2202,57 +2162,57 @@
         <v>6</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1</v>
       </c>
       <c r="B2" s="4">
-        <v>9</v>
-      </c>
-      <c r="C2" s="5">
-        <v>9</v>
+        <v>25</v>
+      </c>
+      <c r="C2" s="7">
+        <v>15</v>
       </c>
       <c r="D2" s="4">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J2" s="17">
         <v>1</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="L2" s="34">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="4">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C3" s="7">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D3" s="6"/>
-      <c r="I3" s="16" t="s">
-        <v>42</v>
+      <c r="I3" s="14" t="s">
+        <v>39</v>
       </c>
       <c r="J3" s="17">
         <v>1</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="L3" s="34">
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.3">
@@ -2260,23 +2220,23 @@
         <v>3</v>
       </c>
       <c r="B4" s="4">
-        <v>15</v>
-      </c>
-      <c r="C4" s="5">
-        <v>12</v>
+        <v>35</v>
+      </c>
+      <c r="C4" s="7">
+        <v>23</v>
       </c>
       <c r="D4" s="6"/>
       <c r="I4" s="16" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="J4" s="17">
         <v>1</v>
       </c>
       <c r="K4" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4">
-        <v>5</v>
+        <v>23</v>
+      </c>
+      <c r="L4" s="34">
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.3">
@@ -2284,191 +2244,138 @@
         <v>4</v>
       </c>
       <c r="B5" s="4">
-        <v>20</v>
-      </c>
-      <c r="C5" s="5">
-        <v>14</v>
+        <v>40</v>
+      </c>
+      <c r="C5" s="7">
+        <v>26</v>
       </c>
       <c r="D5" s="6"/>
       <c r="I5" s="16" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="J5" s="17">
         <v>1</v>
       </c>
       <c r="K5" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="L5" s="34">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>5</v>
       </c>
       <c r="B6" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C6" s="7">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D6" s="6"/>
       <c r="I6" s="16" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="J6" s="17">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="K6" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="L6" s="34">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="4">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C7" s="7">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="D7" s="6"/>
       <c r="I7" s="16" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="J7" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="L7">
+        <v>19</v>
+      </c>
+      <c r="L7" s="34">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="C8" s="7">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="D8" s="6"/>
-      <c r="I8" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" s="17">
-        <v>1</v>
-      </c>
-      <c r="K8" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="16"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="18"/>
+    </row>
+    <row r="9" spans="1:12" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
-      <c r="I9" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="17">
-        <v>1</v>
-      </c>
-      <c r="K9" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="16"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="18"/>
+    </row>
+    <row r="10" spans="1:12" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
-      <c r="I10" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="J10" s="17">
-        <v>1</v>
-      </c>
-      <c r="K10" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="L10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="16"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="18"/>
+    </row>
+    <row r="11" spans="1:12" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
-      <c r="I11" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="J11" s="17">
-        <v>1</v>
-      </c>
-      <c r="K11" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I11" s="16"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="18"/>
+    </row>
+    <row r="12" spans="1:12" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
-      <c r="I12" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="J12" s="17">
-        <v>1</v>
-      </c>
-      <c r="K12" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="L12">
+      <c r="I12" s="16"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="18"/>
+    </row>
+    <row r="13" spans="1:12" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="32" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="53.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="I13" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="J13" s="17">
-        <v>1</v>
-      </c>
-      <c r="K13" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="L13" s="12">
-        <v>8</v>
-      </c>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="12"/>
     </row>
     <row r="14" spans="1:12" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
@@ -2480,18 +2387,9 @@
       <c r="G14" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="I14" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="J14" s="17">
-        <v>1</v>
-      </c>
-      <c r="K14" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="L14">
-        <v>5</v>
-      </c>
+      <c r="I14" s="16"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="18"/>
     </row>
     <row r="15" spans="1:12" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10"/>
@@ -2501,73 +2399,31 @@
       <c r="E15" s="11"/>
       <c r="F15" s="5"/>
       <c r="G15" s="7"/>
-      <c r="I15" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="J15" s="17">
-        <v>1</v>
-      </c>
-      <c r="K15" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="L15" s="25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="28.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="J16" s="17">
-        <v>1</v>
-      </c>
-      <c r="K16" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="L16" s="25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>19</v>
-      </c>
+      <c r="I15" s="16"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="25"/>
+    </row>
+    <row r="16" spans="1:12" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="10"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="11"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="25"/>
+    </row>
+    <row r="17" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="19"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
       <c r="G17" s="20"/>
       <c r="H17" s="21"/>
       <c r="I17" s="21"/>
@@ -2633,14 +2489,14 @@
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
-      <c r="M22" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="N22" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="O22" s="29" t="s">
-        <v>56</v>
+      <c r="M22" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="N22" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="O22" s="27" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:26" ht="14.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2651,14 +2507,14 @@
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
-      <c r="M23" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="N23" s="31">
-        <v>12</v>
-      </c>
-      <c r="O23" s="31">
+      <c r="M23" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="N23" s="29">
         <v>11</v>
+      </c>
+      <c r="O23" s="29">
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
@@ -2669,14 +2525,14 @@
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
-      <c r="M24" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="N24" s="31">
-        <v>12</v>
-      </c>
-      <c r="O24" s="31">
-        <v>15</v>
+      <c r="M24" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="N24" s="29">
+        <v>20</v>
+      </c>
+      <c r="O24" s="29">
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
@@ -2687,14 +2543,14 @@
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
-      <c r="M25" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="N25" s="31">
-        <v>7</v>
-      </c>
-      <c r="O25" s="31">
-        <v>4</v>
+      <c r="M25" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="N25" s="29">
+        <v>15</v>
+      </c>
+      <c r="O25" s="29">
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
@@ -2702,14 +2558,14 @@
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
-      <c r="M26" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="N26" s="31">
-        <v>9</v>
-      </c>
-      <c r="O26" s="31">
-        <v>8</v>
+      <c r="M26" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="N26" s="29">
+        <v>20</v>
+      </c>
+      <c r="O26" s="29">
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
@@ -2717,34 +2573,34 @@
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
-      <c r="M27" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="N27" s="31">
-        <v>16</v>
-      </c>
-      <c r="O27" s="31">
+      <c r="M27" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="N27" s="29">
         <v>15</v>
       </c>
+      <c r="O27" s="29">
+        <v>20</v>
+      </c>
     </row>
     <row r="28" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="M28" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="N28" s="33">
-        <v>56</v>
-      </c>
-      <c r="O28" s="33">
-        <v>53</v>
+      <c r="B28" s="33"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="M28" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="N28" s="31">
+        <v>81</v>
+      </c>
+      <c r="O28" s="31">
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
@@ -2772,25 +2628,25 @@
     </row>
     <row r="30" spans="1:26" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="19" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F30" s="23" t="s">
         <v>16</v>
       </c>
       <c r="G30" s="24" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H30" s="21"/>
       <c r="I30" s="21"/>
@@ -2812,46 +2668,22 @@
       <c r="Y30" s="21"/>
       <c r="Z30" s="21"/>
     </row>
-    <row r="31" spans="1:26" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>19</v>
-      </c>
+    <row r="31" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="19"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="7"/>
       <c r="G31" s="7"/>
     </row>
-    <row r="32" spans="1:26" ht="40.200000000000003" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>19</v>
-      </c>
+    <row r="32" spans="1:26" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="19"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
       <c r="G32" s="7"/>
     </row>
     <row r="33" spans="1:7" ht="13.2" x14ac:dyDescent="0.25">
